--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784664</v>
+        <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>78863</v>
+        <v>92574</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412465</v>
+        <v>412393</v>
       </c>
       <c r="R8" t="n">
-        <v>6967763</v>
+        <v>6967794</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/136828040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784668</v>
+        <v>135784664</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412404</v>
+        <v>412465</v>
       </c>
       <c r="R9" t="n">
-        <v>6967915</v>
+        <v>6967763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784663</v>
+        <v>135784668</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412467</v>
+        <v>412404</v>
       </c>
       <c r="R10" t="n">
-        <v>6967765</v>
+        <v>6967915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784661</v>
+        <v>135784663</v>
       </c>
       <c r="B11" t="n">
-        <v>5498</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412497</v>
+        <v>412467</v>
       </c>
       <c r="R11" t="n">
-        <v>6967725</v>
+        <v>6967765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784662</v>
+        <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>58154</v>
+        <v>80595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412468</v>
+        <v>412385</v>
       </c>
       <c r="R12" t="n">
-        <v>6967764</v>
+        <v>6967787</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,18 +1790,441 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136828038</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, 3m upp i tall.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828038</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784661</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412497</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784661</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784662</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412468</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136828039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6967752</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -1818,6 +2241,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828040</v>
+        <v>135784664</v>
       </c>
       <c r="B8" t="n">
-        <v>92574</v>
+        <v>78863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5467</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412393</v>
+        <v>412465</v>
       </c>
       <c r="R8" t="n">
-        <v>6967794</v>
+        <v>6967763</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828040</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784664</v>
+        <v>135784668</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412465</v>
+        <v>412404</v>
       </c>
       <c r="R9" t="n">
-        <v>6967763</v>
+        <v>6967915</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784668</v>
+        <v>135784663</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412404</v>
+        <v>412467</v>
       </c>
       <c r="R10" t="n">
-        <v>6967915</v>
+        <v>6967765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784663</v>
+        <v>135784661</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>5498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412467</v>
+        <v>412497</v>
       </c>
       <c r="R11" t="n">
-        <v>6967765</v>
+        <v>6967725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828041</v>
+        <v>135784662</v>
       </c>
       <c r="B12" t="n">
-        <v>80595</v>
+        <v>58154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412385</v>
+        <v>412468</v>
       </c>
       <c r="R12" t="n">
-        <v>6967787</v>
+        <v>6967764</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,441 +1790,18 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828041</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>136828038</v>
-      </c>
-      <c r="B13" t="n">
-        <v>58008</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412496</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, 3m upp i tall.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828038</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784661</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5498</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412497</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784662</v>
-      </c>
-      <c r="B15" t="n">
-        <v>58154</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412468</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6967764</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>136828039</v>
-      </c>
-      <c r="B16" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412477</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6967752</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -2241,10 +1818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92574</v>
+        <v>92576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92576</v>
+        <v>92578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92578</v>
+        <v>92579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92579</v>
+        <v>92585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828040</v>
+        <v>135784664</v>
       </c>
       <c r="B8" t="n">
-        <v>92585</v>
+        <v>78863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5467</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412393</v>
+        <v>412465</v>
       </c>
       <c r="R8" t="n">
-        <v>6967794</v>
+        <v>6967763</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828040</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784664</v>
+        <v>135784668</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412465</v>
+        <v>412404</v>
       </c>
       <c r="R9" t="n">
-        <v>6967763</v>
+        <v>6967915</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784668</v>
+        <v>135784663</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412404</v>
+        <v>412467</v>
       </c>
       <c r="R10" t="n">
-        <v>6967915</v>
+        <v>6967765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784663</v>
+        <v>135784661</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>5498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412467</v>
+        <v>412497</v>
       </c>
       <c r="R11" t="n">
-        <v>6967765</v>
+        <v>6967725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828041</v>
+        <v>135784662</v>
       </c>
       <c r="B12" t="n">
-        <v>80602</v>
+        <v>58154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412385</v>
+        <v>412468</v>
       </c>
       <c r="R12" t="n">
-        <v>6967787</v>
+        <v>6967764</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,441 +1790,18 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828041</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>136828038</v>
-      </c>
-      <c r="B13" t="n">
-        <v>58008</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412496</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, 3m upp i tall.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828038</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784661</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5498</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412497</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784662</v>
-      </c>
-      <c r="B15" t="n">
-        <v>58154</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412468</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6967764</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>136828039</v>
-      </c>
-      <c r="B16" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412477</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6967752</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -2241,10 +1818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784664</v>
+        <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>78863</v>
+        <v>92589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412465</v>
+        <v>412393</v>
       </c>
       <c r="R8" t="n">
-        <v>6967763</v>
+        <v>6967794</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/136828040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784668</v>
+        <v>135784664</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412404</v>
+        <v>412465</v>
       </c>
       <c r="R9" t="n">
-        <v>6967915</v>
+        <v>6967763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784663</v>
+        <v>135784668</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412467</v>
+        <v>412404</v>
       </c>
       <c r="R10" t="n">
-        <v>6967765</v>
+        <v>6967915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784661</v>
+        <v>135784663</v>
       </c>
       <c r="B11" t="n">
-        <v>5498</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412497</v>
+        <v>412467</v>
       </c>
       <c r="R11" t="n">
-        <v>6967725</v>
+        <v>6967765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784662</v>
+        <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>58154</v>
+        <v>80604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412468</v>
+        <v>412385</v>
       </c>
       <c r="R12" t="n">
-        <v>6967764</v>
+        <v>6967787</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,18 +1790,441 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136828038</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, 3m upp i tall.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828038</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784661</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412497</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784661</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784662</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412468</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136828039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6967752</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -1818,6 +2241,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828040</v>
+        <v>135784664</v>
       </c>
       <c r="B8" t="n">
-        <v>92589</v>
+        <v>78863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5467</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412393</v>
+        <v>412465</v>
       </c>
       <c r="R8" t="n">
-        <v>6967794</v>
+        <v>6967763</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828040</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784664</v>
+        <v>135784668</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412465</v>
+        <v>412404</v>
       </c>
       <c r="R9" t="n">
-        <v>6967763</v>
+        <v>6967915</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784668</v>
+        <v>135784663</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412404</v>
+        <v>412467</v>
       </c>
       <c r="R10" t="n">
-        <v>6967915</v>
+        <v>6967765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784663</v>
+        <v>135784661</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>5498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412467</v>
+        <v>412497</v>
       </c>
       <c r="R11" t="n">
-        <v>6967765</v>
+        <v>6967725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828041</v>
+        <v>135784662</v>
       </c>
       <c r="B12" t="n">
-        <v>80604</v>
+        <v>58154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412385</v>
+        <v>412468</v>
       </c>
       <c r="R12" t="n">
-        <v>6967787</v>
+        <v>6967764</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,441 +1790,18 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828041</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>136828038</v>
-      </c>
-      <c r="B13" t="n">
-        <v>58008</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412496</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, 3m upp i tall.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828038</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784661</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5498</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412497</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6967725</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784662</v>
-      </c>
-      <c r="B15" t="n">
-        <v>58154</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412468</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6967764</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>136828039</v>
-      </c>
-      <c r="B16" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412477</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6967752</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -2241,10 +1818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784664</v>
+        <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>78863</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412465</v>
+        <v>412393</v>
       </c>
       <c r="R8" t="n">
-        <v>6967763</v>
+        <v>6967794</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,24 +1382,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784664</t>
+          <t>https://artportalen.se/Sighting/136828040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784668</v>
+        <v>135784664</v>
       </c>
       <c r="B9" t="n">
         <v>78863</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412404</v>
+        <v>412465</v>
       </c>
       <c r="R9" t="n">
-        <v>6967915</v>
+        <v>6967763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784668</t>
+          <t>https://artportalen.se/Sighting/135784664</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784663</v>
+        <v>135784668</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412467</v>
+        <v>412404</v>
       </c>
       <c r="R10" t="n">
-        <v>6967765</v>
+        <v>6967915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,16 +1597,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784663</t>
+          <t>https://artportalen.se/Sighting/135784668</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784661</v>
+        <v>135784663</v>
       </c>
       <c r="B11" t="n">
-        <v>5498</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412497</v>
+        <v>412467</v>
       </c>
       <c r="R11" t="n">
-        <v>6967725</v>
+        <v>6967765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784661</t>
+          <t>https://artportalen.se/Sighting/135784663</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784662</v>
+        <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>58154</v>
+        <v>80607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412468</v>
+        <v>412385</v>
       </c>
       <c r="R12" t="n">
-        <v>6967764</v>
+        <v>6967787</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,18 +1790,441 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136828038</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, 3m upp i tall.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828038</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784661</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412497</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967725</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784661</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784662</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412468</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784662</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136828039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6967752</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828039</t>
         </is>
       </c>
     </row>
@@ -1818,6 +2241,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136828038</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136828039</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92604</v>
+        <v>92606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136828038</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136828039</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1836,11 +1836,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
@@ -2152,11 +2148,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92606</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92609</v>
+        <v>92619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136828038</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136828039</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92619</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136828038</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136828039</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92623</v>
+        <v>92625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92625</v>
+        <v>92630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136828038</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136828039</v>
       </c>
       <c r="B16" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47946-2025 artfynd.xlsx
+++ b/artfynd/A 47946-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>136828040</v>
       </c>
       <c r="B8" t="n">
-        <v>92630</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136828041</v>
       </c>
       <c r="B12" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
